--- a/backend/data/price_preprocessing.xlsx
+++ b/backend/data/price_preprocessing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
   <si>
     <t>Price Extraction Data:</t>
   </si>
@@ -59,6 +59,468 @@
   </si>
   <si>
     <t>P11</t>
+  </si>
+  <si>
+    <t>P12</t>
+  </si>
+  <si>
+    <t>P13</t>
+  </si>
+  <si>
+    <t>P14</t>
+  </si>
+  <si>
+    <t>P15</t>
+  </si>
+  <si>
+    <t>P16</t>
+  </si>
+  <si>
+    <t>P17</t>
+  </si>
+  <si>
+    <t>P18</t>
+  </si>
+  <si>
+    <t>P19</t>
+  </si>
+  <si>
+    <t>P20</t>
+  </si>
+  <si>
+    <t>P21</t>
+  </si>
+  <si>
+    <t>P22</t>
+  </si>
+  <si>
+    <t>P23</t>
+  </si>
+  <si>
+    <t>P24</t>
+  </si>
+  <si>
+    <t>P25</t>
+  </si>
+  <si>
+    <t>P26</t>
+  </si>
+  <si>
+    <t>P27</t>
+  </si>
+  <si>
+    <t>P28</t>
+  </si>
+  <si>
+    <t>P29</t>
+  </si>
+  <si>
+    <t>P30</t>
+  </si>
+  <si>
+    <t>P31</t>
+  </si>
+  <si>
+    <t>P32</t>
+  </si>
+  <si>
+    <t>P33</t>
+  </si>
+  <si>
+    <t>P34</t>
+  </si>
+  <si>
+    <t>P35</t>
+  </si>
+  <si>
+    <t>P36</t>
+  </si>
+  <si>
+    <t>P37</t>
+  </si>
+  <si>
+    <t>P38</t>
+  </si>
+  <si>
+    <t>P39</t>
+  </si>
+  <si>
+    <t>P40</t>
+  </si>
+  <si>
+    <t>P41</t>
+  </si>
+  <si>
+    <t>P42</t>
+  </si>
+  <si>
+    <t>P43</t>
+  </si>
+  <si>
+    <t>P44</t>
+  </si>
+  <si>
+    <t>P45</t>
+  </si>
+  <si>
+    <t>P46</t>
+  </si>
+  <si>
+    <t>P47</t>
+  </si>
+  <si>
+    <t>P48</t>
+  </si>
+  <si>
+    <t>P49</t>
+  </si>
+  <si>
+    <t>P50</t>
+  </si>
+  <si>
+    <t>P51</t>
+  </si>
+  <si>
+    <t>P52</t>
+  </si>
+  <si>
+    <t>P53</t>
+  </si>
+  <si>
+    <t>P54</t>
+  </si>
+  <si>
+    <t>P55</t>
+  </si>
+  <si>
+    <t>P56</t>
+  </si>
+  <si>
+    <t>P57</t>
+  </si>
+  <si>
+    <t>P58</t>
+  </si>
+  <si>
+    <t>P59</t>
+  </si>
+  <si>
+    <t>P60</t>
+  </si>
+  <si>
+    <t>P61</t>
+  </si>
+  <si>
+    <t>P62</t>
+  </si>
+  <si>
+    <t>P63</t>
+  </si>
+  <si>
+    <t>P64</t>
+  </si>
+  <si>
+    <t>P65</t>
+  </si>
+  <si>
+    <t>P66</t>
+  </si>
+  <si>
+    <t>P67</t>
+  </si>
+  <si>
+    <t>P68</t>
+  </si>
+  <si>
+    <t>P69</t>
+  </si>
+  <si>
+    <t>P70</t>
+  </si>
+  <si>
+    <t>P71</t>
+  </si>
+  <si>
+    <t>P72</t>
+  </si>
+  <si>
+    <t>P73</t>
+  </si>
+  <si>
+    <t>P74</t>
+  </si>
+  <si>
+    <t>P75</t>
+  </si>
+  <si>
+    <t>P76</t>
+  </si>
+  <si>
+    <t>P77</t>
+  </si>
+  <si>
+    <t>P78</t>
+  </si>
+  <si>
+    <t>P79</t>
+  </si>
+  <si>
+    <t>P80</t>
+  </si>
+  <si>
+    <t>P81</t>
+  </si>
+  <si>
+    <t>P82</t>
+  </si>
+  <si>
+    <t>P83</t>
+  </si>
+  <si>
+    <t>P84</t>
+  </si>
+  <si>
+    <t>P85</t>
+  </si>
+  <si>
+    <t>P86</t>
+  </si>
+  <si>
+    <t>P87</t>
+  </si>
+  <si>
+    <t>P88</t>
+  </si>
+  <si>
+    <t>P89</t>
+  </si>
+  <si>
+    <t>P90</t>
+  </si>
+  <si>
+    <t>P91</t>
+  </si>
+  <si>
+    <t>P92</t>
+  </si>
+  <si>
+    <t>P93</t>
+  </si>
+  <si>
+    <t>P94</t>
+  </si>
+  <si>
+    <t>P95</t>
+  </si>
+  <si>
+    <t>P96</t>
+  </si>
+  <si>
+    <t>P97</t>
+  </si>
+  <si>
+    <t>P98</t>
+  </si>
+  <si>
+    <t>P99</t>
+  </si>
+  <si>
+    <t>P100</t>
+  </si>
+  <si>
+    <t>P101</t>
+  </si>
+  <si>
+    <t>P102</t>
+  </si>
+  <si>
+    <t>P103</t>
+  </si>
+  <si>
+    <t>P104</t>
+  </si>
+  <si>
+    <t>P105</t>
+  </si>
+  <si>
+    <t>P106</t>
+  </si>
+  <si>
+    <t>P107</t>
+  </si>
+  <si>
+    <t>P108</t>
+  </si>
+  <si>
+    <t>P109</t>
+  </si>
+  <si>
+    <t>P110</t>
+  </si>
+  <si>
+    <t>P111</t>
+  </si>
+  <si>
+    <t>P112</t>
+  </si>
+  <si>
+    <t>P113</t>
+  </si>
+  <si>
+    <t>P114</t>
+  </si>
+  <si>
+    <t>P115</t>
+  </si>
+  <si>
+    <t>P116</t>
+  </si>
+  <si>
+    <t>P117</t>
+  </si>
+  <si>
+    <t>P118</t>
+  </si>
+  <si>
+    <t>P119</t>
+  </si>
+  <si>
+    <t>P120</t>
+  </si>
+  <si>
+    <t>P121</t>
+  </si>
+  <si>
+    <t>P122</t>
+  </si>
+  <si>
+    <t>P123</t>
+  </si>
+  <si>
+    <t>P124</t>
+  </si>
+  <si>
+    <t>P125</t>
+  </si>
+  <si>
+    <t>P126</t>
+  </si>
+  <si>
+    <t>P127</t>
+  </si>
+  <si>
+    <t>P128</t>
+  </si>
+  <si>
+    <t>P129</t>
+  </si>
+  <si>
+    <t>P130</t>
+  </si>
+  <si>
+    <t>P131</t>
+  </si>
+  <si>
+    <t>P132</t>
+  </si>
+  <si>
+    <t>P133</t>
+  </si>
+  <si>
+    <t>P134</t>
+  </si>
+  <si>
+    <t>P135</t>
+  </si>
+  <si>
+    <t>P136</t>
+  </si>
+  <si>
+    <t>P137</t>
+  </si>
+  <si>
+    <t>P138</t>
+  </si>
+  <si>
+    <t>P139</t>
+  </si>
+  <si>
+    <t>P140</t>
+  </si>
+  <si>
+    <t>P141</t>
+  </si>
+  <si>
+    <t>P142</t>
+  </si>
+  <si>
+    <t>P143</t>
+  </si>
+  <si>
+    <t>P144</t>
+  </si>
+  <si>
+    <t>P145</t>
+  </si>
+  <si>
+    <t>P146</t>
+  </si>
+  <si>
+    <t>P147</t>
+  </si>
+  <si>
+    <t>P148</t>
+  </si>
+  <si>
+    <t>P149</t>
+  </si>
+  <si>
+    <t>P150</t>
+  </si>
+  <si>
+    <t>P151</t>
+  </si>
+  <si>
+    <t>P152</t>
+  </si>
+  <si>
+    <t>P153</t>
+  </si>
+  <si>
+    <t>P154</t>
+  </si>
+  <si>
+    <t>P155</t>
+  </si>
+  <si>
+    <t>P156</t>
+  </si>
+  <si>
+    <t>P157</t>
+  </si>
+  <si>
+    <t>P158</t>
+  </si>
+  <si>
+    <t>P159</t>
+  </si>
+  <si>
+    <t>P160</t>
+  </si>
+  <si>
+    <t>P161</t>
+  </si>
+  <si>
+    <t>P162</t>
+  </si>
+  <si>
+    <t>P163</t>
+  </si>
+  <si>
+    <t>P164</t>
+  </si>
+  <si>
+    <t>P165</t>
   </si>
 </sst>
 </file>
@@ -416,7 +878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -437,10 +899,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>99900</v>
+        <v>135200</v>
       </c>
       <c r="B4">
-        <v>0.4738505293095276</v>
+        <v>0.09361978964977773</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -448,10 +910,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>166500</v>
+        <v>135200</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0.09361978964977773</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -459,10 +921,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>122850</v>
+        <v>14320</v>
       </c>
       <c r="B6">
-        <v>0.6551587928582715</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -470,10 +932,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>89700</v>
+        <v>135000</v>
       </c>
       <c r="B7">
-        <v>0.3932690788434192</v>
+        <v>0.09346489257888134</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -481,10 +943,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>39920</v>
+        <v>76000</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.04777025666444647</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -492,10 +954,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>43912</v>
+        <v>151920</v>
       </c>
       <c r="B9">
-        <v>0.0315373676726181</v>
+        <v>0.1065691847767159</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
@@ -503,10 +965,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>52712</v>
+        <v>131665</v>
       </c>
       <c r="B10">
-        <v>0.101058619055143</v>
+        <v>0.09088198392168403</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -514,10 +976,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>109200</v>
+        <v>170050</v>
       </c>
       <c r="B11">
-        <v>0.5473218517933323</v>
+        <v>0.1206106042534736</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -525,10 +987,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>109200</v>
+        <v>87246</v>
       </c>
       <c r="B12">
-        <v>0.5473218517933323</v>
+        <v>0.05648011896095045</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -536,10 +998,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>54450</v>
+        <v>66911</v>
       </c>
       <c r="B13">
-        <v>0.1147890662031917</v>
+        <v>0.04073095927756006</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
@@ -547,13 +1009,1707 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>98450</v>
+        <v>151920</v>
       </c>
       <c r="B14">
-        <v>0.4623953231158161</v>
+        <v>0.1065691847767159</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>42500</v>
+      </c>
+      <c r="B15">
+        <v>0.02182499728930126</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>124500</v>
+      </c>
+      <c r="B16">
+        <v>0.08533279635682089</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>66750</v>
+      </c>
+      <c r="B17">
+        <v>0.04060626713548847</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>182427</v>
+      </c>
+      <c r="B18">
+        <v>0.1301964094858966</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>97125</v>
+      </c>
+      <c r="B19">
+        <v>0.06413125977787761</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>57000</v>
+      </c>
+      <c r="B20">
+        <v>0.03305503492928949</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>27420</v>
+      </c>
+      <c r="B21">
+        <v>0.0101457581437135</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>165170</v>
+      </c>
+      <c r="B22">
+        <v>0.1168311157236017</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>128800</v>
+      </c>
+      <c r="B23">
+        <v>0.08866308338109326</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>41650</v>
+      </c>
+      <c r="B24">
+        <v>0.0211666847379916</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>229415</v>
+      </c>
+      <c r="B25">
+        <v>0.1665879273222943</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>41650</v>
+      </c>
+      <c r="B26">
+        <v>0.0211666847379916</v>
+      </c>
+      <c r="C26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>422200</v>
+      </c>
+      <c r="B27">
+        <v>0.3158970863860964</v>
+      </c>
+      <c r="C27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>131646</v>
+      </c>
+      <c r="B28">
+        <v>0.09086726869994888</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>220668</v>
+      </c>
+      <c r="B29">
+        <v>0.1598135039266408</v>
+      </c>
+      <c r="C29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>41650</v>
+      </c>
+      <c r="B30">
+        <v>0.0211666847379916</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>193200</v>
+      </c>
+      <c r="B31">
+        <v>0.1385399402097306</v>
+      </c>
+      <c r="C31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>54280</v>
+      </c>
+      <c r="B32">
+        <v>0.03094843476509859</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>155000</v>
+      </c>
+      <c r="B33">
+        <v>0.1089545996685203</v>
+      </c>
+      <c r="C33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>25415</v>
+      </c>
+      <c r="B34">
+        <v>0.008592915007977198</v>
+      </c>
+      <c r="C34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>22680</v>
+      </c>
+      <c r="B35">
+        <v>0.006474697563469075</v>
+      </c>
+      <c r="C35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>114500</v>
+      </c>
+      <c r="B36">
+        <v>0.07758794281200143</v>
+      </c>
+      <c r="C36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>1305500</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>70875</v>
+      </c>
+      <c r="B38">
+        <v>0.0438010192227265</v>
+      </c>
+      <c r="C38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>193200</v>
+      </c>
+      <c r="B39">
+        <v>0.1385399402097306</v>
+      </c>
+      <c r="C39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>129900</v>
+      </c>
+      <c r="B40">
+        <v>0.0895150172710234</v>
+      </c>
+      <c r="C40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>379588</v>
+      </c>
+      <c r="B41">
+        <v>0.2828947164609117</v>
+      </c>
+      <c r="C41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>407190</v>
+      </c>
+      <c r="B42">
+        <v>0.3042720612153224</v>
+      </c>
+      <c r="C42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>340000</v>
+      </c>
+      <c r="B43">
+        <v>0.2522343902476804</v>
+      </c>
+      <c r="C43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>340000</v>
+      </c>
+      <c r="B44">
+        <v>0.2522343902476804</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>212970</v>
+      </c>
+      <c r="B45">
+        <v>0.1538515156678387</v>
+      </c>
+      <c r="C45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>212970</v>
+      </c>
+      <c r="B46">
+        <v>0.1538515156678387</v>
+      </c>
+      <c r="C46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>212970</v>
+      </c>
+      <c r="B47">
+        <v>0.1538515156678387</v>
+      </c>
+      <c r="C47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>212970</v>
+      </c>
+      <c r="B48">
+        <v>0.1538515156678387</v>
+      </c>
+      <c r="C48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>408744</v>
+      </c>
+      <c r="B49">
+        <v>0.3054756114561873</v>
+      </c>
+      <c r="C49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>24650</v>
+      </c>
+      <c r="B50">
+        <v>0.00800043371179851</v>
+      </c>
+      <c r="C50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>168550</v>
+      </c>
+      <c r="B51">
+        <v>0.1194488762217506</v>
+      </c>
+      <c r="C51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>22680</v>
+      </c>
+      <c r="B52">
+        <v>0.006474697563469075</v>
+      </c>
+      <c r="C52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>134590</v>
+      </c>
+      <c r="B53">
+        <v>0.09314735358354373</v>
+      </c>
+      <c r="C53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>294684</v>
+      </c>
+      <c r="B54">
+        <v>0.2171378119239765</v>
+      </c>
+      <c r="C54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>22680</v>
+      </c>
+      <c r="B55">
+        <v>0.006474697563469075</v>
+      </c>
+      <c r="C55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>74307</v>
+      </c>
+      <c r="B56">
+        <v>0.04645905295930854</v>
+      </c>
+      <c r="C56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>123549</v>
+      </c>
+      <c r="B57">
+        <v>0.08459626078470855</v>
+      </c>
+      <c r="C57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>294400</v>
+      </c>
+      <c r="B58">
+        <v>0.2169178580833036</v>
+      </c>
+      <c r="C58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>41650</v>
+      </c>
+      <c r="B59">
+        <v>0.0211666847379916</v>
+      </c>
+      <c r="C59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>290000</v>
+      </c>
+      <c r="B60">
+        <v>0.2135101225235831</v>
+      </c>
+      <c r="C60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>49000</v>
+      </c>
+      <c r="B61">
+        <v>0.02685915209343391</v>
+      </c>
+      <c r="C61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>135000</v>
+      </c>
+      <c r="B62">
+        <v>0.09346489257888134</v>
+      </c>
+      <c r="C62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>39500</v>
+      </c>
+      <c r="B63">
+        <v>0.01950154122585542</v>
+      </c>
+      <c r="C63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>137970</v>
+      </c>
+      <c r="B64">
+        <v>0.09576511408169272</v>
+      </c>
+      <c r="C64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>63920</v>
+      </c>
+      <c r="B65">
+        <v>0.03841447358230456</v>
+      </c>
+      <c r="C65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>71920</v>
+      </c>
+      <c r="B66">
+        <v>0.04461035641816014</v>
+      </c>
+      <c r="C66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>39015</v>
+      </c>
+      <c r="B67">
+        <v>0.01912591582893167</v>
+      </c>
+      <c r="C67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>35000</v>
+      </c>
+      <c r="B68">
+        <v>0.01601635713068666</v>
+      </c>
+      <c r="C68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>199900</v>
+      </c>
+      <c r="B69">
+        <v>0.1437289920847597</v>
+      </c>
+      <c r="C69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>495000</v>
+      </c>
+      <c r="B70">
+        <v>0.3722796201923821</v>
+      </c>
+      <c r="C70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>17640</v>
+      </c>
+      <c r="B71">
+        <v>0.002571291376880063</v>
+      </c>
+      <c r="C71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
+        <v>41650</v>
+      </c>
+      <c r="B72">
+        <v>0.0211666847379916</v>
+      </c>
+      <c r="C72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>79000</v>
+      </c>
+      <c r="B73">
+        <v>0.05009371272789231</v>
+      </c>
+      <c r="C73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <v>199500</v>
+      </c>
+      <c r="B74">
+        <v>0.1434191979429669</v>
+      </c>
+      <c r="C74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
+        <v>95200</v>
+      </c>
+      <c r="B75">
+        <v>0.06264037547049986</v>
+      </c>
+      <c r="C75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>48000</v>
+      </c>
+      <c r="B76">
+        <v>0.02608466673895196</v>
+      </c>
+      <c r="C76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <v>89100</v>
+      </c>
+      <c r="B77">
+        <v>0.05791601480815998</v>
+      </c>
+      <c r="C77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
+        <v>145000</v>
+      </c>
+      <c r="B78">
+        <v>0.1012097461237008</v>
+      </c>
+      <c r="C78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <v>110000</v>
+      </c>
+      <c r="B79">
+        <v>0.07410275871683267</v>
+      </c>
+      <c r="C79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <v>26397</v>
+      </c>
+      <c r="B80">
+        <v>0.00935345962607847</v>
+      </c>
+      <c r="C80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81">
+        <v>89700</v>
+      </c>
+      <c r="B81">
+        <v>0.05838070602084915</v>
+      </c>
+      <c r="C81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82">
+        <v>135700</v>
+      </c>
+      <c r="B82">
+        <v>0.09400703232701869</v>
+      </c>
+      <c r="C82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83">
+        <v>95200</v>
+      </c>
+      <c r="B83">
+        <v>0.06264037547049986</v>
+      </c>
+      <c r="C83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84">
+        <v>67200</v>
+      </c>
+      <c r="B84">
+        <v>0.04095478554500535</v>
+      </c>
+      <c r="C84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85">
+        <v>39600</v>
+      </c>
+      <c r="B85">
+        <v>0.01957898976130362</v>
+      </c>
+      <c r="C85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86">
+        <v>222300</v>
+      </c>
+      <c r="B86">
+        <v>0.1610774640251553</v>
+      </c>
+      <c r="C86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87">
+        <v>195000</v>
+      </c>
+      <c r="B87">
+        <v>0.1399340138477981</v>
+      </c>
+      <c r="C87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88">
+        <v>110700</v>
+      </c>
+      <c r="B88">
+        <v>0.07464489846497002</v>
+      </c>
+      <c r="C88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89">
+        <v>560000</v>
+      </c>
+      <c r="B89">
+        <v>0.4226211682337087</v>
+      </c>
+      <c r="C89" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90">
+        <v>66911</v>
+      </c>
+      <c r="B90">
+        <v>0.04073095927756006</v>
+      </c>
+      <c r="C90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91">
+        <v>197370</v>
+      </c>
+      <c r="B91">
+        <v>0.1417695441379203</v>
+      </c>
+      <c r="C91" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92">
+        <v>174960</v>
+      </c>
+      <c r="B92">
+        <v>0.1244133273439799</v>
+      </c>
+      <c r="C92" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93">
+        <v>134000</v>
+      </c>
+      <c r="B93">
+        <v>0.09269040722439939</v>
+      </c>
+      <c r="C93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94">
+        <v>283860</v>
+      </c>
+      <c r="B94">
+        <v>0.2087547824470639</v>
+      </c>
+      <c r="C94" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95">
+        <v>231570</v>
+      </c>
+      <c r="B95">
+        <v>0.1682569432612029</v>
+      </c>
+      <c r="C95" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96">
+        <v>231570</v>
+      </c>
+      <c r="B96">
+        <v>0.1682569432612029</v>
+      </c>
+      <c r="C96" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97">
+        <v>136120</v>
+      </c>
+      <c r="B97">
+        <v>0.09433231617590111</v>
+      </c>
+      <c r="C97" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98">
+        <v>54000</v>
+      </c>
+      <c r="B98">
+        <v>0.03073157886584365</v>
+      </c>
+      <c r="C98" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99">
+        <v>199900</v>
+      </c>
+      <c r="B99">
+        <v>0.1437289920847597</v>
+      </c>
+      <c r="C99" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100">
+        <v>39900</v>
+      </c>
+      <c r="B100">
+        <v>0.0198113353676482</v>
+      </c>
+      <c r="C100" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101">
+        <v>25520</v>
+      </c>
+      <c r="B101">
+        <v>0.008674235970197803</v>
+      </c>
+      <c r="C101" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102">
+        <v>202230</v>
+      </c>
+      <c r="B102">
+        <v>0.1455335429607026</v>
+      </c>
+      <c r="C102" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103">
+        <v>247030</v>
+      </c>
+      <c r="B103">
+        <v>0.1802304868414938</v>
+      </c>
+      <c r="C103" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104">
+        <v>261030</v>
+      </c>
+      <c r="B104">
+        <v>0.1910732818042411</v>
+      </c>
+      <c r="C104" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105">
+        <v>319500</v>
+      </c>
+      <c r="B105">
+        <v>0.2363574404808005</v>
+      </c>
+      <c r="C105" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106">
+        <v>259000</v>
+      </c>
+      <c r="B106">
+        <v>0.1895010765346427</v>
+      </c>
+      <c r="C106" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107">
+        <v>259000</v>
+      </c>
+      <c r="B107">
+        <v>0.1895010765346427</v>
+      </c>
+      <c r="C107" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108">
+        <v>105000</v>
+      </c>
+      <c r="B108">
+        <v>0.07023033194442294</v>
+      </c>
+      <c r="C108" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109">
+        <v>140000</v>
+      </c>
+      <c r="B109">
+        <v>0.09733731935129107</v>
+      </c>
+      <c r="C109" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110">
+        <v>101150</v>
+      </c>
+      <c r="B110">
+        <v>0.06724856332966743</v>
+      </c>
+      <c r="C110" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111">
+        <v>65000</v>
+      </c>
+      <c r="B111">
+        <v>0.03925091776514506</v>
+      </c>
+      <c r="C111" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112">
+        <v>44250</v>
+      </c>
+      <c r="B112">
+        <v>0.02318034665964467</v>
+      </c>
+      <c r="C112" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113">
+        <v>52510</v>
+      </c>
+      <c r="B113">
+        <v>0.02957759568766555</v>
+      </c>
+      <c r="C113" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114">
+        <v>367500</v>
+      </c>
+      <c r="B114">
+        <v>0.2735327374959339</v>
+      </c>
+      <c r="C114" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115">
+        <v>312000</v>
+      </c>
+      <c r="B115">
+        <v>0.2305488003221859</v>
+      </c>
+      <c r="C115" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116">
+        <v>89000</v>
+      </c>
+      <c r="B116">
+        <v>0.05783856627271178</v>
+      </c>
+      <c r="C116" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117">
+        <v>89000</v>
+      </c>
+      <c r="B117">
+        <v>0.05783856627271178</v>
+      </c>
+      <c r="C117" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118">
+        <v>126560</v>
+      </c>
+      <c r="B118">
+        <v>0.0869282361870537</v>
+      </c>
+      <c r="C118" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119">
+        <v>188100</v>
+      </c>
+      <c r="B119">
+        <v>0.1345900649018727</v>
+      </c>
+      <c r="C119" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120">
+        <v>1303200</v>
+      </c>
+      <c r="B120">
+        <v>0.9982186836846916</v>
+      </c>
+      <c r="C120" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121">
+        <v>532800</v>
+      </c>
+      <c r="B121">
+        <v>0.4015551665917997</v>
+      </c>
+      <c r="C121" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122">
+        <v>70400</v>
+      </c>
+      <c r="B122">
+        <v>0.04343313867934757</v>
+      </c>
+      <c r="C122" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123">
+        <v>70400</v>
+      </c>
+      <c r="B123">
+        <v>0.04343313867934757</v>
+      </c>
+      <c r="C123" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124">
+        <v>40950</v>
+      </c>
+      <c r="B124">
+        <v>0.02062454498985424</v>
+      </c>
+      <c r="C124" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125">
+        <v>102400</v>
+      </c>
+      <c r="B125">
+        <v>0.06821667002276988</v>
+      </c>
+      <c r="C125" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126">
+        <v>95200</v>
+      </c>
+      <c r="B126">
+        <v>0.06264037547049986</v>
+      </c>
+      <c r="C126" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127">
+        <v>360000</v>
+      </c>
+      <c r="B127">
+        <v>0.2677240973373193</v>
+      </c>
+      <c r="C127" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128">
+        <v>246400</v>
+      </c>
+      <c r="B128">
+        <v>0.1797425610681702</v>
+      </c>
+      <c r="C128" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129">
+        <v>67150</v>
+      </c>
+      <c r="B129">
+        <v>0.04091606127728124</v>
+      </c>
+      <c r="C129" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130">
+        <v>110000</v>
+      </c>
+      <c r="B130">
+        <v>0.07410275871683267</v>
+      </c>
+      <c r="C130" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131">
+        <v>27720</v>
+      </c>
+      <c r="B131">
+        <v>0.01037810375005809</v>
+      </c>
+      <c r="C131" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132">
+        <v>52510</v>
+      </c>
+      <c r="B132">
+        <v>0.02957759568766555</v>
+      </c>
+      <c r="C132" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133">
+        <v>552500</v>
+      </c>
+      <c r="B133">
+        <v>0.4168125280750941</v>
+      </c>
+      <c r="C133" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134">
+        <v>158900</v>
+      </c>
+      <c r="B134">
+        <v>0.1119750925509999</v>
+      </c>
+      <c r="C134" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135">
+        <v>247000</v>
+      </c>
+      <c r="B135">
+        <v>0.1802072522808594</v>
+      </c>
+      <c r="C135" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136">
+        <v>129000</v>
+      </c>
+      <c r="B136">
+        <v>0.08881798045198966</v>
+      </c>
+      <c r="C136" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137">
+        <v>138000</v>
+      </c>
+      <c r="B137">
+        <v>0.09578834864232717</v>
+      </c>
+      <c r="C137" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138">
+        <v>158000</v>
+      </c>
+      <c r="B138">
+        <v>0.1112780557319661</v>
+      </c>
+      <c r="C138" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139">
+        <v>360000</v>
+      </c>
+      <c r="B139">
+        <v>0.2677240973373193</v>
+      </c>
+      <c r="C139" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140">
+        <v>206800</v>
+      </c>
+      <c r="B140">
+        <v>0.1490729410306851</v>
+      </c>
+      <c r="C140" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141">
+        <v>679000</v>
+      </c>
+      <c r="B141">
+        <v>0.5147849254170603</v>
+      </c>
+      <c r="C141" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142">
+        <v>55300</v>
+      </c>
+      <c r="B142">
+        <v>0.03173840982667018</v>
+      </c>
+      <c r="C142" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143">
+        <v>43120</v>
+      </c>
+      <c r="B143">
+        <v>0.02230517820908007</v>
+      </c>
+      <c r="C143" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144">
+        <v>92130</v>
+      </c>
+      <c r="B144">
+        <v>0.06026270543224028</v>
+      </c>
+      <c r="C144" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145">
+        <v>59400</v>
+      </c>
+      <c r="B145">
+        <v>0.03491379978004616</v>
+      </c>
+      <c r="C145" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146">
+        <v>113563</v>
+      </c>
+      <c r="B146">
+        <v>0.07686225003485184</v>
+      </c>
+      <c r="C146" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147">
+        <v>77625</v>
+      </c>
+      <c r="B147">
+        <v>0.04902879536547964</v>
+      </c>
+      <c r="C147" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148">
+        <v>52000</v>
+      </c>
+      <c r="B148">
+        <v>0.02918260815687975</v>
+      </c>
+      <c r="C148" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149">
+        <v>146200</v>
+      </c>
+      <c r="B149">
+        <v>0.1021391285490791</v>
+      </c>
+      <c r="C149" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>195020</v>
+      </c>
+      <c r="B150">
+        <v>0.1399495035548878</v>
+      </c>
+      <c r="C150" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>85020</v>
+      </c>
+      <c r="B151">
+        <v>0.05475611456187363</v>
+      </c>
+      <c r="C151" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>135150</v>
+      </c>
+      <c r="B152">
+        <v>0.09358106538205363</v>
+      </c>
+      <c r="C152" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>199060</v>
+      </c>
+      <c r="B153">
+        <v>0.1430784243869948</v>
+      </c>
+      <c r="C153" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>79000</v>
+      </c>
+      <c r="B154">
+        <v>0.05009371272789231</v>
+      </c>
+      <c r="C154" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155">
+        <v>178000</v>
+      </c>
+      <c r="B155">
+        <v>0.126767762821605</v>
+      </c>
+      <c r="C155" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156">
+        <v>116000</v>
+      </c>
+      <c r="B156">
+        <v>0.07874967084372435</v>
+      </c>
+      <c r="C156" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157">
+        <v>245650</v>
+      </c>
+      <c r="B157">
+        <v>0.1791616970523087</v>
+      </c>
+      <c r="C157" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158">
+        <v>129150</v>
+      </c>
+      <c r="B158">
+        <v>0.08893415325516195</v>
+      </c>
+      <c r="C158" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159">
+        <v>83000</v>
+      </c>
+      <c r="B159">
+        <v>0.0531916541458201</v>
+      </c>
+      <c r="C159" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160">
+        <v>208800</v>
+      </c>
+      <c r="B160">
+        <v>0.150621911739649</v>
+      </c>
+      <c r="C160" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161">
+        <v>94050</v>
+      </c>
+      <c r="B161">
+        <v>0.06174971731284561</v>
+      </c>
+      <c r="C161" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162">
+        <v>131040</v>
+      </c>
+      <c r="B162">
+        <v>0.09039793057513282</v>
+      </c>
+      <c r="C162" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163">
+        <v>314910</v>
+      </c>
+      <c r="B163">
+        <v>0.2328025527037284</v>
+      </c>
+      <c r="C163" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164">
+        <v>125910</v>
+      </c>
+      <c r="B164">
+        <v>0.08642482070664044</v>
+      </c>
+      <c r="C164" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165">
+        <v>170910</v>
+      </c>
+      <c r="B165">
+        <v>0.121276661658328</v>
+      </c>
+      <c r="C165" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166">
+        <v>170910</v>
+      </c>
+      <c r="B166">
+        <v>0.121276661658328</v>
+      </c>
+      <c r="C166" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167">
+        <v>85394</v>
+      </c>
+      <c r="B167">
+        <v>0.05504577208444988</v>
+      </c>
+      <c r="C167" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168">
+        <v>43070</v>
+      </c>
+      <c r="B168">
+        <v>0.02226645394135597</v>
+      </c>
+      <c r="C168" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
